--- a/IPC_División.xlsx
+++ b/IPC_División.xlsx
@@ -418,13 +418,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>0.4374891110214113</v>
+        <v>0.4374891110214112</v>
       </c>
       <c r="C2" s="2">
-        <v>115.3631816630977</v>
+        <v>115.3631816630978</v>
       </c>
       <c r="D2" s="2">
-        <v>0.4374891110214113</v>
+        <v>0.4374891110214112</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -449,7 +449,7 @@
         <v>0.1526772525298325</v>
       </c>
       <c r="C4" s="2">
-        <v>119.0448363503365</v>
+        <v>119.0448363503366</v>
       </c>
       <c r="D4" s="2">
         <v>0.1526772525298325</v>
@@ -463,7 +463,7 @@
         <v>0.2145370383529491</v>
       </c>
       <c r="C5" s="2">
-        <v>113.0320607727496</v>
+        <v>113.03206077275</v>
       </c>
       <c r="D5" s="2">
         <v>0.2145370383529491</v>
